--- a/reports_excel/好好星球_360年中成長評估_【主管評下屬用】Master總表.xlsx
+++ b/reports_excel/好好星球_360年中成長評估_【主管評下屬用】Master總表.xlsx
@@ -213,9 +213,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -271,6 +268,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -718,19 +718,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -748,13 +740,13 @@
           <t>進行部門招募時策略、執行與協調都能夠獨立完成，同時協調其他部門需求，確保招募目標符合所有人想像。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -772,13 +764,13 @@
           <t>酷童工作人員徽章製作時有一些分歧，在決定權上也有些模糊的地方，但我能夠主動提出自己的想法，同時也了解他人的需求後共同產出符合所有人想像的成果。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -796,13 +788,13 @@
           <t>在新的兼職入職後，給予他們方向與目標的指示，其他時候根據他們個人的理解讓他們自行發揮，而並非要求所有事情按照我制定的規則來。而後我會給予最低限度的建議與方向修正，這對我而言是一種接納多元工作方法的表現。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -820,18 +812,18 @@
           <t>因懷孕不適，有不出門辦公的需求，也因此會產生許多仰賴同事的狀況。過往習慣自己把事情都做好，今年則是把自己能夠處理的部分以及能在其他方面彌補他人工作量的地方先規劃好，再學著如何請同事協助。與喻翔曾經有因為請求他協助而有一些摩擦的狀況，但是在彼此溝通後發現彼此之間都有一些沒溝通清楚的地方，經過溝通後最後也讓任務順利完成。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【品牌經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$品牌經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -873,7 +865,7 @@
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>品牌定位與外部溝通一致性</t>
         </is>
@@ -896,19 +888,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>行銷策略與議題倡議</t>
         </is>
@@ -931,19 +923,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>品牌活動策劃與策展敘事</t>
         </is>
@@ -966,19 +958,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>內部品牌管理與雇主品牌</t>
         </is>
@@ -1001,19 +993,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>品牌危機與聲譽風險處理</t>
         </is>
@@ -1036,166 +1028,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -1240,7 +1237,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：胡喻翔（專案經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：4 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：胡喻翔（專案經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$4 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1301,12 +1298,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -1316,28 +1313,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -1347,28 +1344,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -1378,28 +1375,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -1409,28 +1406,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -1440,28 +1437,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -1471,16 +1468,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 10.0</t>
         </is>
@@ -1502,16 +1499,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 10.0, 7.0</t>
         </is>
@@ -1533,16 +1530,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 8.0</t>
         </is>
@@ -1564,16 +1561,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
@@ -1595,16 +1592,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 9.0</t>
         </is>
@@ -1626,16 +1623,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -1657,28 +1654,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -1688,16 +1685,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -2244,142 +2241,142 @@
       <c r="G48" s="5" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -2497,19 +2494,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -2527,13 +2516,13 @@
           <t>在購買教具、道具或各種印刷時，我會先徵詢同事過往的製作經驗作為參考，並評估當下的需求與預算，在不過度煩死同事的情況下獨立採購合理的品項。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2553,13 +2542,13 @@
 我嘗試在每一個設計階段分享成品、同時向大家詳述畫面中分別運用了哪些需要的元素，最後逐步修整成大家可以接受的設計。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -2579,13 +2568,13 @@
 因為無法使用針對兒童教材專業的校色印刷，顏色過濾程度不是很理想，因此來回調整試印了很多顏色，並在「謎題可以被解開」的標準下和酷童夥伴確認成品可接受度，也準備了「萬一有家庭無法透過預設操作方式解謎」的備案，完成了這次的教材。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2603,18 +2592,18 @@
           <t>我盡可能不在工作以外的事項上打擾大家(?)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【美感設計師】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$美感設計師】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -2656,7 +2645,7 @@
       </c>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>品牌識別系統設計與維護</t>
         </is>
@@ -2681,19 +2670,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>視覺與美感設計實務</t>
         </is>
@@ -2716,19 +2705,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求釐清與創意提案</t>
         </is>
@@ -2751,166 +2740,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -2955,7 +2949,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：林文琇（美感設計師） ｜ 直屬主管：何維安 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：林文琇（美感設計師） ｜ 直屬主管：何維安 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3016,12 +3010,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -3031,28 +3025,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -3062,28 +3056,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -3093,28 +3087,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -3124,28 +3118,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -3155,28 +3149,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -3186,16 +3180,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>9.0, 7.0</t>
         </is>
@@ -3217,16 +3211,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -3248,16 +3242,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>9.0, 7.0</t>
         </is>
@@ -3279,16 +3273,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
@@ -3310,16 +3304,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
@@ -3341,16 +3335,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
@@ -3372,28 +3366,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -3403,16 +3397,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0</t>
         </is>
@@ -3819,142 +3813,142 @@
       <c r="G40" s="5" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -4064,19 +4058,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -4094,13 +4080,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -4118,13 +4104,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -4142,13 +4128,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -4166,18 +4152,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【專案經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$專案經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -4219,7 +4205,7 @@
       </c>
     </row>
     <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>專案企劃與現場執行</t>
         </is>
@@ -4241,19 +4227,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案時程與預算規劃管理</t>
         </is>
@@ -4276,19 +4262,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="108" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求研究與方案迭代</t>
         </is>
@@ -4310,19 +4296,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>外部夥伴關係經營</t>
         </is>
@@ -4345,19 +4331,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="126" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>多元教學設計與現場引導</t>
         </is>
@@ -4382,166 +4368,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -4586,7 +4577,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：薛筑瑄（專案經理） ｜ 直屬主管：姚品瑄 ｜ 同儕填答樣本：3 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：薛筑瑄（專案經理） ｜ 直屬主管：姚品瑄 ｜ 同儕填答樣本：$3 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4647,12 +4638,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -4662,28 +4653,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D5" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -4693,28 +4684,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -4724,28 +4715,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>8.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -4755,28 +4746,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>8.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -4786,28 +4777,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -4817,16 +4808,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 10.0</t>
         </is>
@@ -4848,16 +4839,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="D11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -4879,16 +4870,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -4910,16 +4901,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -4941,16 +4932,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
@@ -4972,16 +4963,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -5003,28 +4994,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -5034,16 +5025,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>8.0, 9.0, 10.0</t>
         </is>
@@ -5537,142 +5528,142 @@
       <c r="G45" s="5" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -5787,19 +5778,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -5817,13 +5800,13 @@
           <t>近期「信任」上的展現，我覺得是在品瑄與自身的期待中，我可以依循過去的框架，彈性長出這屆覺察班稍微不太一樣的樣貌，而當我有一些小卡點時，我也能自在地和主管、同儕討論交流，請教他們的觀點，詳細的事件分享如下幾題所述。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -5841,13 +5824,13 @@
           <t>近期的在「多元」上的展現，我覺得很多是在跨部門或與工讀夥伴協作時，練習根據對方的工作習慣與風格，調整我們之間的協作或溝通方式。像是在和品瑄協作時，因為品瑄相對非常熟悉酷童進程與工作項目，所以僅需提供品瑄大框架，再交由其彈性發揮～而如果是和文倩、采妘協作時，我會盡可能提供詳細明確的任務指引與提前對焦。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -5867,13 +5850,13 @@
 以及與品牌夥伴討論覺察班的招募網站框架，今年仍以介紹覺察班為主軸，但是加入了更多整體計畫、對於招募家庭樣貌的描述，在招募資訊比去年更為具體詳細的情況下，我們一起觀察今年的招募報名軌跡，我覺得是很有趣的一次嘗試！（雖然初期報名人數少＆停滯，會讓人感到緊張～～）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="120" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -5892,18 +5875,18 @@
 2. 彈性的人際與工作邊界：我覺得自己的展現是不會過度好奇、介入同事夥伴的私人領域，但我願意在感受到對方（因公 / 私的原因）較忙碌疲憊時，適時關心並詢問我能為其做些什麼。最近一次有印象的故事是筑瑄前陣子病假，向品瑄詢問後與品牌夥伴協助眼界班入學通知的包裝與郵寄。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【專案經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$專案經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -5945,7 +5928,7 @@
       </c>
     </row>
     <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>專案企劃與現場執行</t>
         </is>
@@ -5968,19 +5951,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案時程與預算規劃管理</t>
         </is>
@@ -6003,19 +5986,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="108" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求研究與方案迭代</t>
         </is>
@@ -6037,19 +6020,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>外部夥伴關係經營</t>
         </is>
@@ -6072,19 +6055,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="108" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>社群經營與培力需求回應</t>
         </is>
@@ -6107,166 +6090,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -6311,7 +6299,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：戴佑珍（專案經理） ｜ 直屬主管：姚品瑄 ｜ 同儕填答樣本：3 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：戴佑珍（專案經理） ｜ 直屬主管：姚品瑄 ｜ 同儕填答樣本：$3 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -6372,12 +6360,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -6387,28 +6375,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D5" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -6418,28 +6406,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -6449,28 +6437,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -6480,28 +6468,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -6511,28 +6499,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -6542,16 +6530,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 10.0</t>
         </is>
@@ -6573,16 +6561,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="D11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -6604,16 +6592,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 9.0</t>
         </is>
@@ -6635,16 +6623,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -6666,16 +6654,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 8.0</t>
         </is>
@@ -6697,16 +6685,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -6728,28 +6716,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -6759,16 +6747,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 8.0</t>
         </is>
@@ -7266,142 +7254,142 @@
       <c r="G45" s="5" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -7516,19 +7504,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -7546,13 +7526,13 @@
           <t>在任務交付時完整說明背景脈絡後，交由部屬做出最終決定的主導權，像是在決定策展時，會清楚說明目的以後，讓品牌部門決定哪樣的方案最適合。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -7570,13 +7550,13 @@
           <t>會保持意識自己的位置與個性都比較容易主動表達不同觀點，因此會特意請主管協助我讓比較難表達意見的成員更有機會表達意見與想法，比如特意在討論改變理論的會議中加入「邀請尚未發言的成員」可以發言的角色（VVN）。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -7594,13 +7574,13 @@
           <t>整個NPO EAP的方案即是一種嘗試、修正與反思的過程，過程會有一些錯誤的判斷（比如高估NPO成員對於心理諮商服務的使用率），但有立刻發現後討論修正的方法（比如讓單一使用者從三次使用額度補助調高到六次）。以及積極從方案中獲取使用者的意見，比如當了解有人比較不會使用牌卡，立刻討論明年的規劃是否要拿掉免費贈送的模式，改成補助的模式，減少捐贈資源的浪費。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -7618,18 +7598,18 @@
           <t>當知道 VVN 懷孕時，第一時間選擇讓她改成全遠端，減少懷孕風險，儘管在新人上任時期，也仍選擇尋找兼顧新兵上任的指導需求與讓主管可以安心懷孕的平衡（透過VVN主動有意識與ROO協作共同擔負指導責任）。</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【執行長】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$執行長】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -7671,7 +7651,7 @@
       </c>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>策略決策與組織方向設定</t>
         </is>
@@ -7695,19 +7675,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>組織治理與財務風險管理</t>
         </is>
@@ -7732,19 +7712,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>關鍵利害關係人關係建立與維繫</t>
         </is>
@@ -7768,19 +7748,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>公關、演講與媒體關係</t>
         </is>
@@ -7808,19 +7788,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>核心團隊培養與組織文化建立</t>
         </is>
@@ -7844,166 +7824,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -8048,7 +8033,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：張希慈（執行長） ｜ 直屬主管：董事會 ｜ 同儕填答樣本：0 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：張希慈（執行長） ｜ 直屬主管：董事會 ｜ 同儕填答樣本：$0 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8109,12 +8094,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -8124,34 +8109,34 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -8161,34 +8146,34 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -8198,34 +8183,34 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -8235,34 +8220,34 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -8272,34 +8257,34 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -8309,22 +8294,22 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8346,22 +8331,22 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8383,22 +8368,22 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8420,22 +8405,22 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8457,22 +8442,22 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8494,22 +8479,22 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8531,34 +8516,34 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -8568,22 +8553,22 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8969,142 +8954,142 @@
       <c r="G39" s="5" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -9176,7 +9161,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：何維安（品牌經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：何維安（品牌經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -9237,12 +9222,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -9252,28 +9237,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -9283,28 +9268,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -9314,28 +9299,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -9345,28 +9330,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -9376,28 +9361,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -9407,16 +9392,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
@@ -9438,16 +9423,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
@@ -9469,16 +9454,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -9500,16 +9485,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
@@ -9531,16 +9516,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -9562,16 +9547,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0</t>
         </is>
@@ -9593,28 +9578,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>8.5</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 7.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -9624,16 +9609,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -10077,142 +10062,142 @@
       <c r="G42" s="5" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -10324,19 +10309,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -10355,13 +10332,13 @@
 遇到我不理解的問題(可能是請款、法規或業務工作等等)，我自己會主動先搜尋相關資料，若是無法有明確的答案，會與相關夥伴或會計詢問。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -10379,13 +10356,13 @@
           <t>當討論事情(像是週會討論事項或是品牌跨部門會議)，我也會表達自己的觀點及建議給夥伴們參考，也接納不同的建議及想法，尊重每位夥伴的觀點。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -10403,13 +10380,13 @@
           <t>今年有更多的使用AI來協作工作，像是董事會會議紀錄有先請AI幫我整理，我再做整體調整！請款部分目前還在嘗試有沒有AI可以讓工作流程更順暢的部分。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -10428,18 +10405,18 @@
 我自己平時就會平衡工作與生活，今年也開始做瑜珈運動，做好自我照顧！</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【行政經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$行政經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -10481,7 +10458,7 @@
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>人事薪資與人資系統管理</t>
         </is>
@@ -10505,19 +10482,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>法規與政府公文管理</t>
         </is>
@@ -10541,19 +10518,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>董事會與治理作業執行</t>
         </is>
@@ -10577,19 +10554,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>財務核銷與內控執行</t>
         </is>
@@ -10615,19 +10592,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>總務採購與行政庶務管理</t>
         </is>
@@ -10653,166 +10630,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -10857,7 +10839,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：陳泳璇（行政經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：陳泳璇（行政經理） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10918,12 +10900,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -10933,28 +10915,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="D5" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -10964,28 +10946,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -10995,28 +10977,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -11026,28 +11008,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -11057,28 +11039,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -11088,16 +11070,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11119,16 +11101,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="D11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11150,16 +11132,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11181,16 +11163,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11212,16 +11194,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11243,16 +11225,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>8.0, 10.0</t>
         </is>
@@ -11274,28 +11256,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="D16" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -11305,16 +11287,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
@@ -11768,142 +11750,142 @@
       <c r="G42" s="5" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -12015,19 +11997,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -12045,13 +12019,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -12069,13 +12043,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -12093,13 +12067,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -12117,18 +12091,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【營運經理兼執行長特助】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$營運經理兼執行長特助】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -12170,7 +12144,7 @@
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>組織營運流程設計與優化</t>
         </is>
@@ -12194,19 +12168,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>制度文件與 SOP 建置</t>
         </is>
@@ -12229,19 +12203,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>人力資源策略與選用育留</t>
         </is>
@@ -12265,19 +12239,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>員工關係處理與勞動合規</t>
         </is>
@@ -12300,19 +12274,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>組織文化落實與制度轉化</t>
         </is>
@@ -12335,166 +12309,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -12539,7 +12518,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：張芳媐（營運經理兼執行長特助） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：4 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：張芳媐（營運經理兼執行長特助） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$4 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -12600,12 +12579,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -12615,28 +12594,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -12646,28 +12625,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>8.25</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0, 6.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -12677,28 +12656,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -12708,28 +12687,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -12739,28 +12718,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -12770,16 +12749,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 7.0, 10.0</t>
         </is>
@@ -12801,16 +12780,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -12832,16 +12811,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>9.25</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 8.0</t>
         </is>
@@ -12863,16 +12842,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -12894,16 +12873,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0, 10.0</t>
         </is>
@@ -12925,16 +12904,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
@@ -12956,28 +12935,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.75</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 9.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -12987,16 +12966,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -13541,142 +13520,142 @@
       <c r="G48" s="5" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C53" s="17" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -13794,19 +13773,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -13824,13 +13795,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -13848,13 +13819,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -13872,13 +13843,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -13896,18 +13867,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【部門儲備主管】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$部門儲備主管】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -13949,7 +13920,7 @@
       </c>
     </row>
     <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>部門策略規劃與專案組合管理</t>
         </is>
@@ -13972,19 +13943,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案經理管理與培育</t>
         </is>
@@ -14007,19 +13978,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>部門預算與資源配置管理</t>
         </is>
@@ -14042,19 +14013,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="126" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>跨 LAB 專業掌握（CGL 教育專業與 SL 社群培力）</t>
         </is>
@@ -14077,19 +14048,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>利害關係人管理與衝突協調</t>
         </is>
@@ -14112,166 +14083,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -14316,7 +14292,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：姚品瑄（部門儲備主管） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：3 位 ｜ 自評狀態：尚未自評</t>
+          <t>評估對象：姚品瑄（部門儲備主管） ｜ 直屬主管：張希慈 ｜ 同儕填答樣本：$3 位 ｜ 自評狀態：$尚未自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -14377,12 +14353,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -14392,28 +14368,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="n">
+      <c r="E5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -14423,28 +14399,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -14454,28 +14430,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="D7" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -14485,28 +14461,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -14516,28 +14492,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="D9" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -14547,16 +14523,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="D10" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -14578,16 +14554,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.33</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0, 10.0</t>
         </is>
@@ -14609,16 +14585,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -14640,16 +14616,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="D13" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -14671,16 +14647,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -14702,16 +14678,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -14733,28 +14709,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>9.67</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>9.0, 10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -14764,16 +14740,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="D17" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0, 10.0</t>
         </is>
@@ -15270,142 +15246,142 @@
       <c r="G45" s="5" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
@@ -15520,19 +15496,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -15550,13 +15518,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -15574,13 +15542,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -15598,13 +15566,13 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -15622,18 +15590,18 @@
           <t>（部屬未填寫）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【專案經理】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$專案經理】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -15675,7 +15643,7 @@
       </c>
     </row>
     <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>專案企劃與現場執行</t>
         </is>
@@ -15697,19 +15665,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>專案時程與預算規劃管理</t>
         </is>
@@ -15732,19 +15700,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="108" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求研究與方案迭代</t>
         </is>
@@ -15766,19 +15734,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="15" ht="108" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>外部夥伴關係經營</t>
         </is>
@@ -15801,19 +15769,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="126" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>多元教學設計與現場引導</t>
         </is>
@@ -15838,166 +15806,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
